--- a/EesassinErp/EesassinErp/DownloadMat/EmployeeMasterSampleSheet.xlsx
+++ b/EesassinErp/EesassinErp/DownloadMat/EmployeeMasterSampleSheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20235" windowHeight="6930" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20232" windowHeight="6936" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,64 +14,396 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="81">
   <si>
     <t>Employee Name</t>
   </si>
   <si>
-    <t>Designation</t>
-  </si>
-  <si>
-    <t>D.O.J.</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>Ramesh</t>
-  </si>
-  <si>
-    <t>Engineer</t>
-  </si>
-  <si>
-    <t>IT Department</t>
-  </si>
-  <si>
-    <t>StoreCode</t>
-  </si>
-  <si>
-    <t>0001</t>
+    <t>Employee Designation</t>
+  </si>
+  <si>
+    <t>Employee Department</t>
+  </si>
+  <si>
+    <t>Father/Husband Name</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Marital Status</t>
+  </si>
+  <si>
+    <t>Date of Birth</t>
+  </si>
+  <si>
+    <t>Present Address</t>
+  </si>
+  <si>
+    <t>Permanent Address</t>
+  </si>
+  <si>
+    <t>Aadhar Card Number</t>
+  </si>
+  <si>
+    <t>PAN Number</t>
+  </si>
+  <si>
+    <t>Mobile Number</t>
+  </si>
+  <si>
+    <t>Alternative Mobile Number</t>
+  </si>
+  <si>
+    <t>Employee Email ID</t>
+  </si>
+  <si>
+    <t>Bank Account Number</t>
+  </si>
+  <si>
+    <t>Bank IFSC Code</t>
+  </si>
+  <si>
+    <t>Previous UAN</t>
+  </si>
+  <si>
+    <t>Previous ESI</t>
+  </si>
+  <si>
+    <t>Gross Salary</t>
+  </si>
+  <si>
+    <t>DOJ</t>
+  </si>
+  <si>
+    <t>Name of Nominee</t>
+  </si>
+  <si>
+    <t>Address of Nominee</t>
+  </si>
+  <si>
+    <t>Relation of Nominee</t>
+  </si>
+  <si>
+    <t>DOB of Nominee</t>
+  </si>
+  <si>
+    <t>Store Code</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Rohan Mehta</t>
+  </si>
+  <si>
+    <t>HR Executive</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>Suresh Mehta</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Married</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>1234 5678 9101</t>
+  </si>
+  <si>
+    <t>ABCPM1234A</t>
+  </si>
+  <si>
+    <t>rohan.mehta@abc.com</t>
+  </si>
+  <si>
+    <t>HDFC0001234</t>
+  </si>
+  <si>
+    <t>Nisha Mehta</t>
+  </si>
+  <si>
+    <t>Wife</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Priya Sharma</t>
+  </si>
+  <si>
+    <t>Accountant</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Ramesh Sharma</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>Pune</t>
+  </si>
+  <si>
+    <t>2345 6789 0123</t>
+  </si>
+  <si>
+    <t>PRYSH2345K</t>
+  </si>
+  <si>
+    <t>priya.sharma@abc.com</t>
+  </si>
+  <si>
+    <t>ICIC0002345</t>
+  </si>
+  <si>
+    <t>Sunita Sharma</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>Aman Gupta</t>
+  </si>
+  <si>
+    <t>Store Manager</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>Vinod Gupta</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>3456 7890 1234</t>
+  </si>
+  <si>
+    <t>AMNGP3456L</t>
+  </si>
+  <si>
+    <t>aman.gupta@abc.com</t>
+  </si>
+  <si>
+    <t>SBIN0003456</t>
+  </si>
+  <si>
+    <t>Neha Gupta</t>
+  </si>
+  <si>
+    <t>Sneha Iyer</t>
+  </si>
+  <si>
+    <t>Software Engineer</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Mahesh Iyer</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>4567 8901 2345</t>
+  </si>
+  <si>
+    <t>SNEHI4567M</t>
+  </si>
+  <si>
+    <t>sneha.iyer@abc.com</t>
+  </si>
+  <si>
+    <t>KKBK0004567</t>
+  </si>
+  <si>
+    <t>Rekha Iyer</t>
+  </si>
+  <si>
+    <t>00002462</t>
+  </si>
+  <si>
+    <t>LeavingDate</t>
+  </si>
+  <si>
+    <t>PFAccount</t>
+  </si>
+  <si>
+    <t>RefEmployeeCode</t>
+  </si>
+  <si>
+    <t>RefEmployeeCode1</t>
+  </si>
+  <si>
+    <t>RefEmployeeCode2</t>
+  </si>
+  <si>
+    <t>RefEmployeeCode3</t>
+  </si>
+  <si>
+    <t>RefEmployeeCode4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -80,12 +412,179 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7EDEC"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -98,41 +597,229 @@
       <right/>
       <top/>
       <bottom style="thick">
-        <color rgb="FFC0CAD5"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="41"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="41" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="43">
+    <cellStyle name="20% - Accent1" xfId="18" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="22" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="26" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="30" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="34" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="19" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="23" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="27" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="31" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="35" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="39" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="20" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="24" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="28" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="32" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="36" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="40" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="17" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="21" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="25" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="29" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="33" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="37" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="15" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="41"/>
+    <cellStyle name="Note 2" xfId="42"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="16" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="14">
     <dxf>
@@ -312,7 +999,7 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="2" defaultTableStyle="Normal Style 1 - Accent 1" defaultPivotStyle="Light Style 1 - Accent 1">
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
@@ -539,149 +1226,666 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:AC13"/>
+  <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" customWidth="1"/>
-    <col min="4" max="4" width="29.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="9"/>
+    <col min="1" max="1" width="51.88671875" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21" style="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="7" customFormat="1" ht="15" thickBot="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:29" s="3" customFormat="1" ht="13.8">
+      <c r="A1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
+      <c r="J1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>75</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" ht="13.5" thickTop="1">
+    <row r="2" spans="1:29" ht="26.4">
       <c r="A2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
-        <v>45187</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+        <v>77</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="8">
+        <v>33372</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="7">
+        <v>9876543210</v>
+      </c>
+      <c r="N2" s="7">
+        <v>9876500001</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" s="11">
+        <v>100012345678</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" s="11">
+        <v>101201020101</v>
+      </c>
+      <c r="S2" s="7">
+        <v>9876543</v>
+      </c>
+      <c r="T2" s="7">
+        <v>45000</v>
+      </c>
+      <c r="U2" s="8">
+        <v>44265</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y2" s="8">
+        <v>34171</v>
+      </c>
+      <c r="Z2" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB2" s="8">
+        <v>45859</v>
+      </c>
+      <c r="AC2">
+        <v>1234</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" ht="12.75">
-      <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+    <row r="3" spans="1:29" ht="26.4">
+      <c r="A3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="8">
+        <v>34571</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" s="7">
+        <v>9823456789</v>
+      </c>
+      <c r="N3" s="7">
+        <v>9812345670</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="P3" s="11">
+        <v>200045678912</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="R3" s="11">
+        <v>101201020102</v>
+      </c>
+      <c r="S3" s="7">
+        <v>9876544</v>
+      </c>
+      <c r="T3" s="7">
+        <v>40000</v>
+      </c>
+      <c r="U3" s="8">
+        <v>44606</v>
+      </c>
+      <c r="V3" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="W3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="X3" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y3" s="8">
+        <v>24212</v>
+      </c>
+      <c r="Z3" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC3">
+        <v>12345</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" ht="12.75">
-      <c r="B4" s="1"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+    <row r="4" spans="1:29" ht="26.4">
+      <c r="A4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="8">
+        <v>32396</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="M4" s="7">
+        <v>9811112233</v>
+      </c>
+      <c r="N4" s="7">
+        <v>9999991111</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="P4" s="11">
+        <v>300078901234</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R4" s="11">
+        <v>101201020103</v>
+      </c>
+      <c r="S4" s="7">
+        <v>9876545</v>
+      </c>
+      <c r="T4" s="7">
+        <v>55000</v>
+      </c>
+      <c r="U4" s="8">
+        <v>43770</v>
+      </c>
+      <c r="V4" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="W4" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="X4" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y4" s="8">
+        <v>32906</v>
+      </c>
+      <c r="Z4" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC4">
+        <v>23456</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" ht="12.75">
-      <c r="B5" s="1"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+    <row r="5" spans="1:29" ht="26.4">
+      <c r="A5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="8">
+        <v>35082</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="M5" s="7">
+        <v>9845012345</v>
+      </c>
+      <c r="N5" s="7">
+        <v>9845011111</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="P5" s="11">
+        <v>400045678912</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="R5" s="11">
+        <v>101201020104</v>
+      </c>
+      <c r="S5" s="7">
+        <v>9876546</v>
+      </c>
+      <c r="T5" s="7">
+        <v>60000</v>
+      </c>
+      <c r="U5" s="8">
+        <v>45078</v>
+      </c>
+      <c r="V5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="X5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y5" s="8">
+        <v>25090</v>
+      </c>
+      <c r="Z5" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB5" s="8">
+        <v>45859</v>
+      </c>
+      <c r="AC5">
+        <v>34567</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" ht="12.75">
-      <c r="B6" s="1"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+    <row r="6" spans="1:29" ht="13.2">
+      <c r="A6" s="3"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="7"/>
     </row>
-    <row r="7" spans="1:8" ht="12.75">
-      <c r="B7" s="1"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
+    <row r="7" spans="1:29" ht="13.2">
+      <c r="A7" s="3"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="7"/>
     </row>
-    <row r="8" spans="1:8" ht="12.75">
-      <c r="B8" s="1"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+    <row r="8" spans="1:29" ht="13.2">
+      <c r="A8" s="3"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="7"/>
     </row>
-    <row r="9" spans="1:8" ht="12.75">
-      <c r="B9" s="1"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+    <row r="9" spans="1:29" ht="13.2">
+      <c r="A9" s="3"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="7"/>
     </row>
-    <row r="10" spans="1:8" ht="12.75">
-      <c r="B10" s="1"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
+    <row r="10" spans="1:29" ht="13.2">
+      <c r="A10" s="3"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="7"/>
     </row>
-    <row r="11" spans="1:8" ht="12.75">
-      <c r="B11" s="1"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+    <row r="11" spans="1:29" ht="13.2">
+      <c r="A11" s="3"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="9"/>
+      <c r="AA11" s="7"/>
     </row>
-    <row r="12" spans="1:8" ht="12.75">
+    <row r="12" spans="1:29" ht="13.2">
       <c r="B12" s="1"/>
       <c r="C12" s="2"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="8"/>
+      <c r="E12" s="4"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:8" ht="12.75">
+    <row r="13" spans="1:29" ht="13.2">
       <c r="B13" s="1"/>
       <c r="C13" s="2"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="8"/>
+      <c r="E13" s="4"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
